--- a/reconcile/src/product_classification.xlsx
+++ b/reconcile/src/product_classification.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C61BAC-ACDC-A846-BE6B-C6BDA3439B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0611C4E-8724-7E4B-ADBA-ED5202D2E20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1060" windowWidth="27640" windowHeight="16940" xr2:uid="{FEFD0C4C-127E-084E-B8EE-D2E1A58B5722}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="816">
   <si>
     <t>product</t>
   </si>
@@ -4272,6 +4272,9 @@
       <c r="A161" s="2" t="s">
         <v>164</v>
       </c>
+      <c r="B161" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
